--- a/content/Question Bank/MCQ/Python/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 11 - File Handling/Unit 11 - File Handling - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 11" sheetId="1" r:id="R4d5a91fcc0c84828"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 11" sheetId="1" r:id="R95d6be2d6fdb43f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -405,15 +405,17 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="18" customHeight="1">
+    <x:row r="2" ht="60" hidden="0" customHeight="1">
       <x:c r="A2" s="1" t="str">
         <x:v>Python - MCQ - 11.1.1</x:v>
       </x:c>
       <x:c r="B2" s="1" t="str">
-        <x:v>A game keeps the player's score only in a variable. Every restart resets it to zero. Which change gives the score persistence?</x:v>
+        <x:v>Make a score survive the end of the program
+A game stores the current score in a variable, but the score disappears whenever the program closes. The next run must recover the previous value.
+Which change provides persistence?</x:v>
       </x:c>
       <x:c r="C2" s="2" t="str">
-        <x:v>Variables live only while a program runs. Writing the score to a file places it on disk so a later run can read it back.</x:v>
+        <x:v>File data remains on disk after the process ends, while ordinary variables exist only during execution.</x:v>
       </x:c>
       <x:c r="D2" s="4" t="n">
         <x:v>1</x:v>
@@ -425,7 +427,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G2" s="2" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H2" s="1" t="str">
         <x:v>python - Set 1</x:v>
@@ -441,30 +443,32 @@
       </x:c>
       <x:c r="L2" s="1"/>
       <x:c r="M2" s="1" t="str">
-        <x:v>Keep the program continuously running so its memory is never released</x:v>
+        <x:v>Assign the score to a second variable before exiting.</x:v>
       </x:c>
       <x:c r="N2" s="1" t="str">
-        <x:v>Write the score to a file and read it on the next run</x:v>
+        <x:v>Persist the score in a file and reload it.</x:v>
       </x:c>
       <x:c r="O2" s="1" t="str">
-        <x:v>Rename the score variable</x:v>
+        <x:v>Print the score twice before closing.</x:v>
       </x:c>
       <x:c r="P2" s="1" t="str">
-        <x:v>Place the score inside a loop</x:v>
+        <x:v>Store the score in a loop variable.</x:v>
       </x:c>
       <x:c r="Q2" s="4" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="18" customHeight="1">
+    <x:row r="3" ht="60" hidden="0" customHeight="1">
       <x:c r="A3" s="1" t="str">
         <x:v>Python - MCQ - 11.1.2</x:v>
       </x:c>
       <x:c r="B3" s="1" t="str">
-        <x:v>A report should be written and closed automatically when its block ends. Which opening statement has the correct structure?</x:v>
+        <x:v>Choose the read shape required by a validator
+A validator must compare every saved wristband line by line and also retain all lines as a list for later indexing.
+Which reading operation directly returns that required list shape?</x:v>
       </x:c>
       <x:c r="C3" s="2" t="str">
-        <x:v>`with open(...) as file:` creates a context-managed file. Python closes it when the indented block ends, even if the block exits because of an error.</x:v>
+        <x:v>`readlines()` returns a list containing one string per line, including stored line endings.</x:v>
       </x:c>
       <x:c r="D3" s="4" t="n">
         <x:v>1</x:v>
@@ -473,10 +477,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H3" s="1" t="str">
         <x:v>python - Set 1</x:v>
@@ -488,34 +492,44 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K3" s="1" t="str">
-        <x:v>context-managed-files</x:v>
+        <x:v>file-operations</x:v>
       </x:c>
       <x:c r="L3" s="1"/>
       <x:c r="M3" s="1" t="str">
-        <x:v>`open with 'report.txt' as file:`</x:v>
+        <x:v>`file.write("all lines")`</x:v>
       </x:c>
       <x:c r="N3" s="1" t="str">
-        <x:v>`with file = open('report.txt', 'w'):`</x:v>
+        <x:v>`file.read()`</x:v>
       </x:c>
       <x:c r="O3" s="1" t="str">
-        <x:v>`using open('report.txt', 'w') as file:`</x:v>
+        <x:v>`file.close()`</x:v>
       </x:c>
       <x:c r="P3" s="1" t="str">
-        <x:v>`with open('report.txt', 'w') as file:`</x:v>
+        <x:v>`file.readlines()`</x:v>
       </x:c>
       <x:c r="Q3" s="4" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="198" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Python - MCQ - 11.1.3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>A reports folder contains CSV, TXT, and JSON files. Which glob pattern selects every CSV file directly inside that folder?</x:v>
+        <x:v>Trace two file modes applied in sequence
+A daily log already contains `OLD
+`. A reset step is followed by two new scans.
+```python
+with open("log.txt", "w", encoding="utf-8") as file:
+    file.write("A101\n")
+with open("log.txt", "a", encoding="utf-8") as file:
+    file.write("A102\n")
+    file.write("A103\n")
+```
+Which final content should the audit expect?</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>The `*` wildcard matches any filename portion within one folder level. `*.csv` therefore selects filenames ending in `.csv`.</x:v>
+        <x:v>The first open in write mode erases the old content; append mode then preserves A101 and adds two lines.</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:v>1</x:v>
@@ -524,7 +538,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G4" t="str">
         <x:v>apply</x:v>
@@ -539,42 +553,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K4" t="str">
-        <x:v>glob-pattern-matching</x:v>
+        <x:v>file-operations</x:v>
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4" t="str">
-        <x:v>`*.csv`</x:v>
+        <x:v>`A101\nA102\nA103\n`</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>`**.txt`</x:v>
+        <x:v>`OLD\nA101\nA102\nA103\n`</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>`csv.*`</x:v>
+        <x:v>`A103\n`</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>`*.json`</x:v>
+        <x:v>`OLD\nA102\nA103\n`</x:v>
       </x:c>
       <x:c r="Q4" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="66" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Python - MCQ - 11.1.4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>A scanner writes two IDs and reads them as separate lines.
-```python
-with open('ids.txt', 'w') as file:
-    file.write('A1\nA2\n')
-with open('ids.txt', 'r') as file:
-    lines = file.readlines()
-print(lines)
-```
-What is displayed?</x:v>
+        <x:v>Guarantee closure when processing fails
+A report may encounter a calculation failure after opening a file. The file must still be closed when control leaves the writing block.
+Which structure supplies that guarantee?</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>`readlines()` returns one string per line and keeps each trailing newline. Both saved lines therefore include `\n` in the list representation.</x:v>
+        <x:v>A `with` block releases the file whether the block completes normally or exits because of an error.</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:v>1</x:v>
@@ -586,7 +594,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G5" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H5" t="str">
         <x:v>python - Set 1</x:v>
@@ -598,34 +606,41 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K5" t="str">
-        <x:v>file-operations</x:v>
+        <x:v>context-managed-files</x:v>
       </x:c>
       <x:c r="L5"/>
       <x:c r="M5" t="str">
-        <x:v>`['A1', 'A2']`</x:v>
+        <x:v>Open the file globally and never close it.</x:v>
       </x:c>
       <x:c r="N5" t="str">
-        <x:v>`'A1\nA2\n'` returned as one string</x:v>
+        <x:v>Put `file.close()` after the line that may terminate execution.</x:v>
       </x:c>
       <x:c r="O5" t="str">
-        <x:v>`['A1\n', 'A2\n']`</x:v>
+        <x:v>Use `with open(...) as file:` for the file operation.</x:v>
       </x:c>
       <x:c r="P5" t="str">
-        <x:v>`[A1, A2]`</x:v>
+        <x:v>Open the same file a second time after the calculation.</x:v>
       </x:c>
       <x:c r="Q5" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>Python - MCQ - 11.1.5</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>A script must build a cross-platform path to `reports/day1.txt` without manually inserting a slash. Which expression is appropriate?</x:v>
+        <x:v>Build a path without guessing the operating system's separator
+A report must be stored as `reports/daily.txt` on Windows, macOS, and Linux without manually concatenating slashes.
+```python
+from pathlib import Path
+folder = Path("reports")
+report = ________
+```
+Which expression completes the path safely?</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>`Path('reports') / 'day1.txt'` joins path components using `pathlib`, which handles operating-system path details.</x:v>
+        <x:v>`Path` uses `/` to join path components correctly for the current operating system.</x:v>
       </x:c>
       <x:c r="D6" t="n">
         <x:v>1</x:v>
@@ -653,30 +668,32 @@
       </x:c>
       <x:c r="L6"/>
       <x:c r="M6" t="str">
-        <x:v>`Path('reports').split('day1.txt')`</x:v>
+        <x:v>`folder / "daily.txt"`</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>`Path('reports') / 'day1.txt'`</x:v>
+        <x:v>`folder.divide("daily.txt")`</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>`Path('reports') + Path('day1.txt')`</x:v>
+        <x:v>`folder + "/" + "daily.txt"`</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>`open('reports') / 'day1.txt'`</x:v>
+        <x:v>`"reports" * "daily.txt"`</x:v>
       </x:c>
       <x:c r="Q6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="66" hidden="0" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>Python - MCQ - 11.1.6</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>A sales CSV has headers `item,quantity,price`. The code should read `row['quantity']` instead of remembering that quantity is column 1. Which reader supports that design?</x:v>
+        <x:v>Select all CSV files in one reports folder
+A reports folder contains several file types. A script needs every filename ending in `.csv` directly inside that folder.
+Which pattern describes that set?</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>`csv.DictReader` uses the header row as dictionary keys. Each data row can then be accessed by meaningful column names.</x:v>
+        <x:v>`*` matches any filename characters within the current folder, followed by the required `.csv` suffix.</x:v>
       </x:c>
       <x:c r="D7" t="n">
         <x:v>1</x:v>
@@ -685,10 +702,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F7" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G7" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H7" t="str">
         <x:v>python - Set 1</x:v>
@@ -700,34 +717,40 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>csv-processing</x:v>
+        <x:v>glob-pattern-matching</x:v>
       </x:c>
       <x:c r="L7"/>
       <x:c r="M7" t="str">
-        <x:v>`csv.DictReader(file)`</x:v>
+        <x:v>`**.txt`</x:v>
       </x:c>
       <x:c r="N7" t="str">
-        <x:v>`file.readlines()`</x:v>
+        <x:v>`csv.*`</x:v>
       </x:c>
       <x:c r="O7" t="str">
-        <x:v>`csv.writer(file)`</x:v>
+        <x:v>`*.csv`</x:v>
       </x:c>
       <x:c r="P7" t="str">
-        <x:v>`json.load(file)` with automatic CSV header mapping</x:v>
+        <x:v>`csv`</x:v>
       </x:c>
       <x:c r="Q7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="132" hidden="0" customHeight="1">
       <x:c r="A8" t="str">
         <x:v>Python - MCQ - 11.1.7</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>A fest report contains dictionaries nested inside dictionaries. Why is JSON a better storage choice than CSV for this data?</x:v>
+        <x:v>Correct arithmetic performed on CSV text
+A sales calculation reads quantity and price with `csv.DictReader`. The row looks numeric in the file, but multiplication does not behave as intended because CSV values arrive as text.
+```python
+row = {"item": "Mug", "quantity": "2", "price": "150"}
+total = row["quantity"] * row["price"]
+```
+Which smallest repair produces numeric `300`?</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>JSON represents nested dictionaries and lists directly. CSV is naturally flat and table-shaped, so it cannot preserve the same nested structure cleanly.</x:v>
+        <x:v>Each CSV field must be converted separately from text to an integer before arithmetic.</x:v>
       </x:c>
       <x:c r="D8" t="n">
         <x:v>1</x:v>
@@ -736,7 +759,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F8" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G8" t="str">
         <x:v>analyze</x:v>
@@ -751,34 +774,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>json-processing</x:v>
+        <x:v>csv-processing</x:v>
       </x:c>
       <x:c r="L8"/>
       <x:c r="M8" t="str">
-        <x:v>CSV cannot store any text</x:v>
+        <x:v>`total = str(row["quantity"]) * str(row["price"])`</x:v>
       </x:c>
       <x:c r="N8" t="str">
-        <x:v>JSON automatically encrypts every value</x:v>
+        <x:v>`total = row["quantity"] + row["price"]`</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>CSV always converts numbers to zero</x:v>
+        <x:v>`total = int(row["quantity"] * row["price"])`</x:v>
       </x:c>
       <x:c r="P8" t="str">
-        <x:v>JSON naturally preserves nested data structures</x:v>
+        <x:v>`total = int(row["quantity"]) * int(row["price"])`</x:v>
       </x:c>
       <x:c r="Q8" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="66" hidden="0" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>Python - MCQ - 11.1.8</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>`attendees.txt` already contains 80 IDs. A registration script opens it with mode `'w'` before writing one new ID. What is the consequence?</x:v>
+        <x:v>Preserve a nested stall report across runs
+A report is a dictionary whose stall names map to inner item-price dictionaries. It must be saved and restored with its nesting intact.
+Which format and module best match that shape?</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Write mode truncates an existing file immediately. The previous IDs are erased, and the file contains only what the new session writes.</x:v>
+        <x:v>JSON naturally represents nested dictionaries and lists and reconstructs them as Python structures.</x:v>
       </x:c>
       <x:c r="D9" t="n">
         <x:v>1</x:v>
@@ -787,10 +812,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F9" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G9" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H9" t="str">
         <x:v>python - Set 1</x:v>
@@ -802,41 +827,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K9" t="str">
-        <x:v>file-operations</x:v>
+        <x:v>json-processing</x:v>
       </x:c>
       <x:c r="L9"/>
       <x:c r="M9" t="str">
-        <x:v>The new ID is rejected</x:v>
+        <x:v>Plain text with manual string splitting</x:v>
       </x:c>
       <x:c r="N9" t="str">
-        <x:v>The old and new IDs are merged automatically</x:v>
+        <x:v>JSON using Python's `json` module</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>The existing content is erased before the new write</x:v>
+        <x:v>CSV with one unlabelled cell</x:v>
       </x:c>
       <x:c r="P9" t="str">
-        <x:v>Python changes the mode to append</x:v>
+        <x:v>A variable that is never written to disk</x:v>
       </x:c>
       <x:c r="Q9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="66" hidden="0" customHeight="1">
       <x:c r="A10" t="str">
         <x:v>Python - MCQ - 11.1.9</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>A report crashes inside a managed file block.
-```python
-with open('report.txt', 'w') as file:
-    file.write('Line 1\n')
-    value = 10 / 0
-    file.write('Line 2\n')
-```
-Which statement describes the file state?</x:v>
+        <x:v>Defend a read and preserve a rupee symbol
+A receipt file may not exist on a teammate's machine, and when it does exist it can contain `₹`. Unit 12 exception handling is not yet available.
+Which approach addresses both risks using only Unit 11 tools?</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>The division raises `ZeroDivisionError`, so the second write never runs. The context manager still closes the file, preserving the first line written before the failure.</x:v>
+        <x:v>The existence guard prevents a missing-file read, while explicit UTF-8 keeps character interpretation consistent.</x:v>
       </x:c>
       <x:c r="D10" t="n">
         <x:v>1</x:v>
@@ -860,34 +880,41 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>context-managed-files</x:v>
+        <x:v>file-errors</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10" t="str">
-        <x:v>Both lines are written before the error appears</x:v>
+        <x:v>Check existence before reading and use UTF-8 explicitly.</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>The file is closed and contains only Line 1</x:v>
+        <x:v>Open blindly in write mode so a missing file is replaced.</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>The file remains open with both lines</x:v>
+        <x:v>Remove every non-English character before saving.</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>The file is deleted automatically</x:v>
+        <x:v>Use `readlines()` without checking the path or encoding.</x:v>
       </x:c>
       <x:c r="Q10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>Python - MCQ - 11.1.10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>A receipt reader must avoid crashing when a file is absent and must preserve a rupee symbol across different machines. Which approach addresses both risks within this unit's scope?</x:v>
+        <x:v>Keep individual lines clean while streaming a large file
+A very large attendee file should be processed one line at a time rather than loaded fully into memory. Stored newline characters must not remain in the IDs.
+```python
+with open("attendees.txt", "r", encoding="utf-8") as file:
+    for line in file:
+        attendee_id = ________
+```
+Which expression completes the cleanup?</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>`Path.exists()` can guard the read before opening a missing file, while explicit UTF-8 on both writes and reads keeps character interpretation consistent.</x:v>
+        <x:v>Direct iteration streams one line at a time, and `rstrip("\r\n")` removes line-ending characters without deleting meaningful spaces elsewhere in the ID.</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>1</x:v>
@@ -896,10 +923,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F11" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H11" t="str">
         <x:v>python - Set 1</x:v>
@@ -911,34 +938,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>file-errors</x:v>
+        <x:v>file-operations</x:v>
       </x:c>
       <x:c r="L11"/>
       <x:c r="M11" t="str">
-        <x:v>Check `Path.exists()` first and use `encoding='utf-8'` consistently</x:v>
+        <x:v>`line.lstrip()`</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Use write mode for every read</x:v>
+        <x:v>`line.replace(" ", "")`</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Remove all non-English characters</x:v>
+        <x:v>`line.rstrip("\r\n")`</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>Assume every machine uses the same default encoding</x:v>
+        <x:v>`line.split(",")`</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="66" hidden="0" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Python - MCQ - 11.2.1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>A developer needs the complete contents of a small text file as one string. Which file method directly provides that shape?</x:v>
+        <x:v>Put separate IDs on separate lines
+A wristband logger writes one ID per call. The file currently stores `A101A102` on one line because `write()` adds no separator automatically.
+Which write preserves the intended line structure?</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>`read()` returns the entire remaining file contents as one string, including any embedded newline characters.</x:v>
+        <x:v>The newline must be included explicitly in the string passed to `write()`.</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>1</x:v>
@@ -950,7 +979,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>python - Set 2</x:v>
@@ -966,30 +995,32 @@
       </x:c>
       <x:c r="L12"/>
       <x:c r="M12" t="str">
-        <x:v>`writelines()`</x:v>
+        <x:v>`file.write("A103")`</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>`readlines()`</x:v>
+        <x:v>`file.writelines(["A103"])`</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>`read()`</x:v>
+        <x:v>`file.write("A103" + "")`</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>`write()`</x:v>
+        <x:v>`file.write("A103\n")`</x:v>
       </x:c>
       <x:c r="Q12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="66" hidden="0" customHeight="1">
       <x:c r="A13" t="str">
         <x:v>Python - MCQ - 11.2.2</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>A multi-gigabyte log should be processed without loading every line into a list first. Which pattern is most memory-efficient?</x:v>
+        <x:v>Process a huge log without constructing a list of every line
+A multi-gigabyte log needs one validation check per line, and no later step needs all lines in memory together.
+Which approach is most appropriate?</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Looping directly over the open file yields one line at a time. It avoids storing the entire file or a full list of lines in memory.</x:v>
+        <x:v>Direct iteration reads incrementally and avoids storing the entire file or line list at once.</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>1</x:v>
@@ -998,10 +1029,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F13" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>python - Set 2</x:v>
@@ -1017,30 +1048,32 @@
       </x:c>
       <x:c r="L13"/>
       <x:c r="M13" t="str">
-        <x:v>Call `read()` twice</x:v>
+        <x:v>Call `read()` and split the resulting whole-file string.</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>Call `readlines()` before the loop</x:v>
+        <x:v>Loop directly over the open file object.</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Convert the file to JSON first</x:v>
+        <x:v>Call `readlines()` before beginning the loop.</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>Use `for line in file:`</x:v>
+        <x:v>Open the file in append mode.</x:v>
       </x:c>
       <x:c r="Q13" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="66" hidden="0" customHeight="1">
       <x:c r="A14" t="str">
         <x:v>Python - MCQ - 11.2.3</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>A file loop receives the line `'A101\n'`, but the ID must be compared as `'A101'`. Which expression removes the surrounding whitespace?</x:v>
+        <x:v>Repair a `writelines` call that merges records
+A batch save uses `writelines(["A101", "A102", "A103"])`, producing one run-together line.
+Which replacement preserves one ID per line?</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>`line.strip()` removes leading and trailing whitespace, including the newline at the end of a file line.</x:v>
+        <x:v>Like `write`, `writelines` adds no line separators; each supplied string must contain its own newline.</x:v>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>1</x:v>
@@ -1052,7 +1085,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>python - Set 2</x:v>
@@ -1068,30 +1101,32 @@
       </x:c>
       <x:c r="L14"/>
       <x:c r="M14" t="str">
-        <x:v>`line.strip()`</x:v>
+        <x:v>`file.writelines("A101", "A102", "A103")`</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>`line.append()`</x:v>
+        <x:v>`file.writelines(["A101", "A102", "A103"], separator="\n")`</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>`line.readlines()`</x:v>
+        <x:v>`file.writelines(["A101\n", "A102\n", "A103\n"])`</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>`line.close()`</x:v>
+        <x:v>`file.readlines(["A101", "A102", "A103"])`</x:v>
       </x:c>
       <x:c r="Q14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="66" hidden="0" customHeight="1">
       <x:c r="A15" t="str">
         <x:v>Python - MCQ - 11.2.4</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>A writer calls `file.write('A1')` followed by `file.write('A2')`. No newline characters are supplied. What text is stored?</x:v>
+        <x:v>Identify the mode that quietly destroys earlier records
+`audit.txt` initially contains three records. A function intended to add a fourth opens the file with mode `"w"` and writes one new line.
+Which diagnosis and smallest repair are both correct?</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>`write()` adds no separator or line break automatically. The two strings are written consecutively as `A1A2`.</x:v>
+        <x:v>`"w"` empties an existing file on open, whereas `"a"` keeps its contents and writes at the end.</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:v>1</x:v>
@@ -1100,10 +1135,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F15" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>python - Set 2</x:v>
@@ -1119,30 +1154,37 @@
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15" t="str">
-        <x:v>A1 and A2 on separate lines</x:v>
+        <x:v>`"w"` truncates the file; change the mode to `"a"`.</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>`A1A2`</x:v>
+        <x:v>Write mode preserves old lines; the defect is a missing `read()`.</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Only A2</x:v>
+        <x:v>Append mode would delete the file, so use read mode.</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>`A1 A2` with an automatic space</x:v>
+        <x:v>All three modes behave identically when the file exists.</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>Python - MCQ - 11.2.5</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>A developer uses `file.writelines(['A1', 'A2', 'A3'])` and expects three lines. Why do the values run together?</x:v>
+        <x:v>Verify the resource state after a normal `with` block
+A test checks whether a file object has been released immediately after the indented `with` block ends.
+```python
+with open("report.txt", "w", encoding="utf-8") as file:
+    file.write("Ready")
+closed_state = file.closed
+```
+Which value is stored in `closed_state`?</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>`writelines()` writes the supplied strings in sequence but does not insert newline characters. Each list element must already contain its required `\n`.</x:v>
+        <x:v>The object name remains accessible, but its managed file resource has already been closed.</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>1</x:v>
@@ -1154,7 +1196,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G16" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H16" t="str">
         <x:v>python - Set 2</x:v>
@@ -1166,34 +1208,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>file-operations</x:v>
+        <x:v>context-managed-files</x:v>
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>The list must contain integers</x:v>
+        <x:v>`False`, until `file.close()` is called manually</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>`writelines()` accepts only one value</x:v>
+        <x:v>`True`; leaving the `with` block closes the file</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Append mode disables line breaks</x:v>
+        <x:v>`None`, because `closed` is a method</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>The strings do not include their own newline characters</x:v>
+        <x:v>The name `file` is deleted when the block ends</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="66" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Python - MCQ - 11.2.6</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>A log starts with `Gate open\n`. The script then opens it in append mode and writes `First scan\n`. What remains in the file?</x:v>
+        <x:v>Create a report path from folder and filename objects
+A script already imports `Path` and wants a portable path object for `reports/summary.txt`.
+Which expression creates it directly?</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Append mode preserves existing content and adds new text at the end. Both log entries remain in their original order.</x:v>
+        <x:v>A `Path` object supports `/` for portable component joining.</x:v>
       </x:c>
       <x:c r="D17" t="n">
         <x:v>1</x:v>
@@ -1202,10 +1246,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>apply</x:v>
+        <x:v>understand</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>python - Set 2</x:v>
@@ -1217,34 +1261,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>file-operations</x:v>
+        <x:v>file-paths</x:v>
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>Only `First scan`</x:v>
+        <x:v>`Path.join("reports", "summary.txt")`</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>An empty file</x:v>
+        <x:v>`"reports" / "summary.txt"`</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>`Gate open` followed by `First scan`</x:v>
+        <x:v>`Path("reports") + Path("summary.txt")`</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>Only `Gate open`</x:v>
+        <x:v>`Path("reports") / "summary.txt"`</x:v>
       </x:c>
       <x:c r="Q17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="66" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Python - MCQ - 11.2.7</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>An existing report contains important data. A script executes `file = open('report.txt', 'w')` but crashes before calling `write`. What happened to the old content?</x:v>
+        <x:v>Extract filename details without splitting strings
+A classifier receives `Path("reports/day1_sales.csv")` and needs the full filename, base name, and extension.
+Which triple is correct for `(path.name, path.stem, path.suffix)`?</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Opening an existing file in write mode truncates it immediately. The old content is already gone even though no new write completed.</x:v>
+        <x:v>`name` includes the extension, `stem` removes it, and `suffix` includes the leading dot.</x:v>
       </x:c>
       <x:c r="D18" t="n">
         <x:v>1</x:v>
@@ -1256,7 +1302,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G18" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H18" t="str">
         <x:v>python - Set 2</x:v>
@@ -1268,34 +1314,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>file-operations</x:v>
+        <x:v>file-paths</x:v>
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18" t="str">
-        <x:v>It remains until the first successful write</x:v>
+        <x:v>`("day1_sales.csv", "day1_sales", ".csv")`</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>It is erased when the file opens in write mode</x:v>
+        <x:v>`("reports", "day1_sales.csv", "csv")`</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>It moves to a backup file</x:v>
+        <x:v>`("day1_sales", ".csv", "reports")`</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>Python silently switches to read mode</x:v>
+        <x:v>`("reports/day1_sales.csv", "reports", "day1_sales")`</x:v>
       </x:c>
       <x:c r="Q18" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="66" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>Python - MCQ - 11.2.8</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>Why is `with open(...) as file:` preferred over a manual `open()` and later `close()` pair?</x:v>
+        <x:v>Complete a recursive search without changing result types
+Existing code expects `Path` objects and currently uses `reports.glob("*.txt")`, which misses text files in deeper folders. The replacement must remain a `pathlib` operation and search every depth.
+Which replacement satisfies both requirements?</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>The context manager closes the file whenever the block exits, including error paths where a later manual `close()` would never be reached.</x:v>
+        <x:v>`Path.rglob("*.txt")` searches recursively and continues yielding `Path` objects, preserving the interface expected by later code.</x:v>
       </x:c>
       <x:c r="D19" t="n">
         <x:v>1</x:v>
@@ -1304,10 +1352,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H19" t="str">
         <x:v>python - Set 2</x:v>
@@ -1319,40 +1367,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>context-managed-files</x:v>
+        <x:v>glob-pattern-matching</x:v>
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19" t="str">
-        <x:v>It guarantees the file is closed when the block exits</x:v>
+        <x:v>`glob.glob("reports/**/*.txt")` without enabling recursive matching</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>It makes every file read-only</x:v>
+        <x:v>`reports.glob("*.txt")` followed by converting each result to a string</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>It prevents all runtime errors</x:v>
+        <x:v>`reports.rglob("*.txt")`</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>It automatically converts text to CSV</x:v>
+        <x:v>`reports.iterdir()` with no traversal of child folders</x:v>
       </x:c>
       <x:c r="Q19" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="66" hidden="0" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>Python - MCQ - 11.2.9</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>A script checks a file object immediately after its `with` block.
-```python
-with open('note.txt', 'w') as file:
-    file.write('saved')
-print(file.closed)
-```
-What is printed?</x:v>
+        <x:v>Read named CSV columns without memorising positions
+A sales file has headers `item,quantity,price`, and the processing code should use expressions such as `row["price"]`.
+Which reader supplies each row in that form?</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>The context manager closes the file as soon as the indented block ends. Its `closed` attribute is therefore `True`.</x:v>
+        <x:v>`DictReader` uses the header row as keys and returns each data row as a dictionary.</x:v>
       </x:c>
       <x:c r="D20" t="n">
         <x:v>1</x:v>
@@ -1364,7 +1408,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G20" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H20" t="str">
         <x:v>python - Set 2</x:v>
@@ -1376,34 +1420,42 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>context-managed-files</x:v>
+        <x:v>csv-processing</x:v>
       </x:c>
       <x:c r="L20"/>
       <x:c r="M20" t="str">
-        <x:v>saved</x:v>
+        <x:v>`csv.reader(file)`</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>False</x:v>
+        <x:v>`csv.DictReader(file)`</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>True</x:v>
+        <x:v>`csv.DictWriter(file, fieldnames=...)`</x:v>
       </x:c>
       <x:c r="P20" t="str">
-        <x:v>None</x:v>
+        <x:v>`csv.writer(file)`</x:v>
       </x:c>
       <x:c r="Q20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A21" t="str">
         <x:v>Python - MCQ - 11.2.10</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>For `Path('reports/day1_sales.csv')`, which property returns only `.csv`?</x:v>
+        <x:v>Complete a CSV export with a header and ordered fields
+A list of sale dictionaries must become a CSV with columns ordered as `item`, `quantity`, and `price`, including one header row.
+```python
+fieldnames = ["item", "quantity", "price"]
+writer = csv.DictWriter(file, fieldnames=fieldnames)
+________
+writer.writerows(sales)
+```
+Which missing line produces the required header exactly once?</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>A Path object's `.suffix` property returns the final file extension including its leading dot.</x:v>
+        <x:v>`writeheader()` writes the configured field names as the CSV header before the data rows.</x:v>
       </x:c>
       <x:c r="D21" t="n">
         <x:v>1</x:v>
@@ -1412,7 +1464,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F21" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G21" t="str">
         <x:v>apply</x:v>
@@ -1427,34 +1479,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>file-paths</x:v>
+        <x:v>csv-processing</x:v>
       </x:c>
       <x:c r="L21"/>
       <x:c r="M21" t="str">
-        <x:v>`.name`</x:v>
+        <x:v>`writer.writerow(fieldnames)`</x:v>
       </x:c>
       <x:c r="N21" t="str">
-        <x:v>The `.stem` property without an extension</x:v>
+        <x:v>`writer.writerows(sales)`</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>`.parent`</x:v>
+        <x:v>`writer.writerow(sales[0])`</x:v>
       </x:c>
       <x:c r="P21" t="str">
-        <x:v>`.suffix`</x:v>
+        <x:v>`writer.writeheader()`</x:v>
       </x:c>
       <x:c r="Q21" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="66" hidden="0" customHeight="1">
       <x:c r="A22" t="str">
         <x:v>Python - MCQ - 11.3.1</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>A report path should be assembled from a folder object and a filename. Which `pathlib` expression is correct?</x:v>
+        <x:v>Convert a Python structure to JSON text in memory
+An application needs JSON text to send elsewhere, but it does not want to open a file.
+Which function returns a JSON string?</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Path objects use `/` to join path components safely. The result points to `reports/summary.txt` using the current platform's path rules.</x:v>
+        <x:v>The `s` in `dumps` indicates conversion from a Python object to a JSON string.</x:v>
       </x:c>
       <x:c r="D22" t="n">
         <x:v>1</x:v>
@@ -1463,10 +1517,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F22" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H22" t="str">
         <x:v>python - Set 3</x:v>
@@ -1478,34 +1532,41 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>file-paths</x:v>
+        <x:v>json-processing</x:v>
       </x:c>
       <x:c r="L22"/>
       <x:c r="M22" t="str">
-        <x:v>`Path('reports') / 'summary.txt'`</x:v>
+        <x:v>`json.dump(data, file)`</x:v>
       </x:c>
       <x:c r="N22" t="str">
-        <x:v>`Path('reports').append('summary.txt')`</x:v>
+        <x:v>`json.load(file)`</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>`Path('reports') * 'summary.txt'`</x:v>
+        <x:v>`json.dumps(data)`</x:v>
       </x:c>
       <x:c r="P22" t="str">
-        <x:v>`'reports'.Path('summary.txt')`</x:v>
+        <x:v>`json.loads(data)`</x:v>
       </x:c>
       <x:c r="Q22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A23" t="str">
         <x:v>Python - MCQ - 11.3.2</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>A setup command may run repeatedly, but it should create `reports` only when needed and not fail if it already exists. Which call fits?</x:v>
+        <x:v>Account for a tuple after a JSON round trip
+A location is stored as a Python tuple, converted to JSON text, and then loaded back. The program must know whether tuple identity survives.
+```python
+import json
+original = {"location": (15.2, 74.1)}
+restored = json.loads(json.dumps(original))
+```
+Which value and type does `restored["location"]` have?</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>`Path('reports').mkdir(exist_ok=True)` creates the folder and suppresses the already-exists error on later runs.</x:v>
+        <x:v>JSON represents both Python lists and tuples as arrays, which load back into Python as lists.</x:v>
       </x:c>
       <x:c r="D23" t="n">
         <x:v>1</x:v>
@@ -1517,7 +1578,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H23" t="str">
         <x:v>python - Set 3</x:v>
@@ -1529,34 +1590,40 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>file-paths</x:v>
+        <x:v>json-processing</x:v>
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
-        <x:v>`Path('reports').write_text('create the folder now')`</x:v>
+        <x:v>`[15.2, 74.1]`, a list</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>`Path('reports').exists(False)`</x:v>
+        <x:v>`(15.2, 74.1)`, a tuple</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>`Path('reports').mkdir(exist_ok=True)`</x:v>
+        <x:v>`"(15.2, 74.1)"`, a string</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>`open('reports', 'a')`</x:v>
+        <x:v>`None`</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="132" hidden="0" customHeight="1">
       <x:c r="A24" t="str">
         <x:v>Python - MCQ - 11.3.3</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>A small text file should be overwritten and then read back using only its Path object. Which method pair performs those whole-file operations?</x:v>
+        <x:v>Repair confusion between a JSON file and a JSON string
+A configuration file is already open, but the code passes that file object to the function intended for a string.
+```python
+with open("config.json", "r", encoding="utf-8") as file:
+    config = json.loads(file)
+```
+Which smallest repair uses the open file correctly?</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>`write_text()` writes the entire text content, and `read_text()` reads the entire file back. Both are convenient Path methods for small text files.</x:v>
+        <x:v>`load` reads JSON from an open file; `loads` parses JSON text held in a string.</x:v>
       </x:c>
       <x:c r="D24" t="n">
         <x:v>1</x:v>
@@ -1565,10 +1632,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F24" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G24" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H24" t="str">
         <x:v>python - Set 3</x:v>
@@ -1580,34 +1647,42 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>file-paths</x:v>
+        <x:v>json-processing</x:v>
       </x:c>
       <x:c r="L24"/>
       <x:c r="M24" t="str">
-        <x:v>`write()` and `readlines()` on a manually opened file</x:v>
+        <x:v>Replace `loads` with `dumps`.</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>`write_text()` and `read_text()`</x:v>
+        <x:v>Replace the file mode with `"a"`.</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>`dump()` and `load()`</x:v>
+        <x:v>Convert the file object to `str(file)`.</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>`writerow()` and `reader()`</x:v>
+        <x:v>Use `json.load(file)` instead.</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A25" t="str">
         <x:v>Python - MCQ - 11.3.4</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>Before reading an optional daily log, a script asks whether the path is present. Which method performs that check?</x:v>
+        <x:v>Check for an optional file before opening it
+A report may not have been generated yet. The script should test for it before attempting a read.
+```python
+from pathlib import Path
+report = Path("daily.txt")
+if ________:
+    text = report.read_text(encoding="utf-8")
+```
+Which condition fills the blank?</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>`Path.exists()` returns whether the referenced file or folder currently exists, allowing a simple conditional guard.</x:v>
+        <x:v>`Path.exists()` checks whether the target is present without opening it.</x:v>
       </x:c>
       <x:c r="D25" t="n">
         <x:v>1</x:v>
@@ -1619,7 +1694,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H25" t="str">
         <x:v>python - Set 3</x:v>
@@ -1635,30 +1710,32 @@
       </x:c>
       <x:c r="L25"/>
       <x:c r="M25" t="str">
-        <x:v>`Path.read()`</x:v>
+        <x:v>`report.is_dir()`</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>`Path.opened()`</x:v>
+        <x:v>`report.exists()`</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>`Path.available()`</x:v>
+        <x:v>`report.parent.exists()`</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>`Path.exists()`</x:v>
+        <x:v>`bool(report.name)`</x:v>
       </x:c>
       <x:c r="Q25" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="66" hidden="0" customHeight="1">
       <x:c r="A26" t="str">
         <x:v>Python - MCQ - 11.3.5</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>A reports folder contains `day1.csv`, `day2.csv`, and `notes.txt`. Which pattern selects exactly the CSV files in that folder?</x:v>
+        <x:v>Predict the first failure when reading a missing path
+A script assumes `day4.txt` exists and opens it in read mode, but the file has never been created.
+Which execution account is correct?</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>`*.csv` accepts any filename prefix but requires the `.csv` suffix, so the TXT note is excluded.</x:v>
+        <x:v>Read mode requires an existing file; it does not create one.</x:v>
       </x:c>
       <x:c r="D26" t="n">
         <x:v>1</x:v>
@@ -1682,34 +1759,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>glob-pattern-matching</x:v>
+        <x:v>file-errors</x:v>
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26" t="str">
-        <x:v>`day*.txt`</x:v>
+        <x:v>`open("day4.txt", "r")` raises `FileNotFoundError` immediately.</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>`**/*.txt`</x:v>
+        <x:v>Read mode creates an empty file and returns an empty string.</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>`*.csv`</x:v>
+        <x:v>Python silently changes the mode to append.</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>`csv.*`</x:v>
+        <x:v>The failure occurs only when the program later closes the file.</x:v>
       </x:c>
       <x:c r="Q26" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" hidden="0" customHeight="1">
       <x:c r="A27" t="str">
         <x:v>Python - MCQ - 11.3.6</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>A data folder contains text files both at its top level and inside nested subfolders. Which Path glob searches every level?</x:v>
+        <x:v>Keep text encoding consistent across machines
+A receipt containing `₹` is written on one operating system and read on another. The two operations must agree on character encoding.
+Which practice gives the clearest portable contract?</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>The double asterisk crosses directory levels. `**/*.txt` finds text files directly inside the starting folder and beneath its subfolders.</x:v>
+        <x:v>Explicit UTF-8 makes both operations use the same broad, predictable character mapping.</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:v>1</x:v>
@@ -1721,7 +1800,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H27" t="str">
         <x:v>python - Set 3</x:v>
@@ -1733,34 +1812,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>glob-pattern-matching</x:v>
+        <x:v>file-errors</x:v>
       </x:c>
       <x:c r="L27"/>
       <x:c r="M27" t="str">
-        <x:v>`**/*.txt`</x:v>
+        <x:v>Use the system default on writing and guess on reading.</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>`*.txt` only</x:v>
+        <x:v>Remove the symbol before writing.</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>`txt/**`</x:v>
+        <x:v>Use UTF-8 explicitly for both operations.</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>`*/.txt`</x:v>
+        <x:v>Open the text file in CSV mode.</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" hidden="0" customHeight="1">
       <x:c r="A28" t="str">
         <x:v>Python - MCQ - 11.3.7</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>A developer switches from `glob.glob(pattern)` to `Path(folder).glob(pattern)`. What important result-type difference should the code expect?</x:v>
+        <x:v>Extend a log across repeated program runs
+Each run of a scanner should add one new wristband ID while keeping every ID written by earlier runs.
+Which mode should the scanner use?</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>The standalone function returns matching path strings. `Path.glob()` integrates with pathlib and yields Path objects.</x:v>
+        <x:v>Append mode writes at the end of an existing file and creates it when absent.</x:v>
       </x:c>
       <x:c r="D28" t="n">
         <x:v>1</x:v>
@@ -1769,10 +1850,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H28" t="str">
         <x:v>python - Set 3</x:v>
@@ -1784,34 +1865,42 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>glob-pattern-matching</x:v>
+        <x:v>file-operations</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28" t="str">
-        <x:v>Both always return open file objects</x:v>
+        <x:v>`"r"`</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>`Path.glob()` returns only folder names</x:v>
+        <x:v>`"a"`</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>`glob.glob()` returns dictionaries</x:v>
+        <x:v>`"w"`</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>`Path.glob()` yields Path objects while `glob.glob()` returns strings</x:v>
+        <x:v>No mode, because every mode appends</x:v>
       </x:c>
       <x:c r="Q28" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>Python - MCQ - 11.3.8</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>A script hard-codes three sales filenames. A fourth daily file is later added and silently ignored. Why is a glob pattern a better design?</x:v>
+        <x:v>Account for a crash inside a managed write
+A report writes one line, encounters an unrelated division-by-zero error, and has a second write below the failing line.
+```python
+with open("report.txt", "w", encoding="utf-8") as file:
+    file.write("Before\n")
+    value = 10 / 0
+    file.write("After\n")
+```
+Which account best describes the file-handling behaviour?</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>A glob describes the filename shape rather than a fixed list. New files matching that shape are discovered without changing the code.</x:v>
+        <x:v>A context manager guarantees cleanup but does not suppress this error or execute skipped statements.</x:v>
       </x:c>
       <x:c r="D29" t="n">
         <x:v>1</x:v>
@@ -1820,10 +1909,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H29" t="str">
         <x:v>python - Set 3</x:v>
@@ -1835,34 +1924,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>glob-pattern-matching</x:v>
+        <x:v>context-managed-files</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29" t="str">
-        <x:v>It converts every file to JSON</x:v>
+        <x:v>The error is suppressed, and both lines are written.</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>It discovers newly added files that match the stated pattern</x:v>
+        <x:v>The file remains open because the block did not finish normally.</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>It guarantees files contain valid data</x:v>
+        <x:v>The second write runs during automatic cleanup.</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>It sorts file contents automatically</x:v>
+        <x:v>Error propagates; the file closes; the second write is skipped.</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="66" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>Python - MCQ - 11.3.9</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>A CSV row contains quantity `'2'` and price `'350'`. The code uses `row['quantity'] * row['price']`. What correction is required for revenue arithmetic?</x:v>
+        <x:v>Choose between CSV and JSON from the data shape
+Dataset A is a flat table of sales rows. Dataset B is a dictionary of stalls, each containing its own item dictionary.
+Which pairing is most suitable?</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>CSV readers return fields as strings. Both numeric fields must be converted, such as with `int(...)`, before multiplying them.</x:v>
+        <x:v>CSV fits flat rows and columns, while JSON naturally preserves nested structure.</x:v>
       </x:c>
       <x:c r="D30" t="n">
         <x:v>1</x:v>
@@ -1871,10 +1962,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H30" t="str">
         <x:v>python - Set 3</x:v>
@@ -1886,34 +1977,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>csv-processing</x:v>
+        <x:v>json-processing</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>Convert both fields to numbers before multiplication</x:v>
+        <x:v>JSON for A only; plain variables for B</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>Use `strip()` on only the price</x:v>
+        <x:v>CSV for both because all files are text</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Replace DictReader with JSON dump</x:v>
+        <x:v>CSV for A and JSON for B</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>Open the CSV in append mode</x:v>
+        <x:v>JSON for A and CSV for B because nesting belongs in columns</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="66" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>Python - MCQ - 11.3.10</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>A list of sales dictionaries must be written with columns in the order item, quantity, price. Which writer setup provides named-column control?</x:v>
+        <x:v>Create a reports folder safely on repeated runs
+A startup step may run many times. It should create `reports/` when absent and do nothing harmful when the folder already exists.
+Which statement matches that requirement?</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>`csv.DictWriter` accepts `fieldnames` to define the CSV column order. `writeheader()` then writes those names as the header row.</x:v>
+        <x:v>`mkdir(exist_ok=True)` creates the directory or leaves the existing one in place without an error.</x:v>
       </x:c>
       <x:c r="D31" t="n">
         <x:v>1</x:v>
@@ -1937,34 +2030,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>csv-processing</x:v>
+        <x:v>file-paths</x:v>
       </x:c>
       <x:c r="L31"/>
       <x:c r="M31" t="str">
-        <x:v>`csv.reader(file)`</x:v>
+        <x:v>`Path("reports").mkdir(exist_ok=True)`</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>`csv.DictWriter(file, fieldnames=['item', 'quantity', 'price'])`</x:v>
+        <x:v>`Path("reports").mkdir(exist_ok=False)`</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>`json.DictWriter(file, fieldnames=['item', 'quantity', 'price'])` as a CSV substitute</x:v>
+        <x:v>`Path("reports").touch(exist_ok=True)`</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>`file.readlines(fieldnames)`</x:v>
+        <x:v>`Path("reports").parent.mkdir(exist_ok=True)`</x:v>
       </x:c>
       <x:c r="Q31" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="66" hidden="0" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>Python - MCQ - 11.4.1</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>A `DictWriter` writes data rows correctly, but the resulting file has no header. Which call was most likely omitted?</x:v>
+        <x:v>Account for the result type of two glob interfaces
+One implementation uses `Path("reports").glob("*.csv")`; another uses `glob.glob("reports/*.csv")`. Later code depends on whether results are path objects or strings.
+Which comparison is accurate?</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>Creating a DictWriter does not automatically emit the header. Calling `writer.writeheader()` writes the field names once before the data rows.</x:v>
+        <x:v>The two interfaces match similar patterns but represent their matched locations differently.</x:v>
       </x:c>
       <x:c r="D32" t="n">
         <x:v>1</x:v>
@@ -1976,7 +2071,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G32" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H32" t="str">
         <x:v>python - Set 4</x:v>
@@ -1988,34 +2083,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K32" t="str">
-        <x:v>csv-processing</x:v>
+        <x:v>glob-pattern-matching</x:v>
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32" t="str">
-        <x:v>`writer.writerow([])`</x:v>
+        <x:v>Both return file contents instead of names.</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>`writer.readheader()`</x:v>
+        <x:v>`Path.glob()` yields `Path`; `glob.glob()` yields strings.</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>`file.header = True` before writing all rows</x:v>
+        <x:v>`glob.glob()` returns dictionaries keyed by extension.</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>`writer.writeheader()`</x:v>
+        <x:v>`Path.glob()` opens every matching file automatically.</x:v>
       </x:c>
       <x:c r="Q32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="66" hidden="0" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>Python - MCQ - 11.4.2</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>A developer has an open JSON file and also a JSON-formatted string. Which pairing reads both into Python objects correctly?</x:v>
+        <x:v>Choose the filename that defeats a numeric assumption
+A developer assumes `day*_sales.txt` selects only filenames whose middle section is a day number. A test must demonstrate that `*` is not a numeric validator.
+Which additional filename is the clearest counterexample?</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>`json.load(file)` reads from an open file object, while `json.loads(text)` parses a JSON string. The `s` form is the string form.</x:v>
+        <x:v>`day_final_sales.txt` satisfies the literal prefix and suffix because `*` accepts `final` just as readily as digits.</x:v>
       </x:c>
       <x:c r="D33" t="n">
         <x:v>1</x:v>
@@ -2027,7 +2124,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>python - Set 4</x:v>
@@ -2039,34 +2136,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K33" t="str">
-        <x:v>json-processing</x:v>
+        <x:v>glob-pattern-matching</x:v>
       </x:c>
       <x:c r="L33"/>
       <x:c r="M33" t="str">
-        <x:v>Use `loads` for both inputs</x:v>
+        <x:v>`day1_sales.csv`</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>Use `dump` for the file and `dumps` for the string</x:v>
+        <x:v>`week1_sales.txt`</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Use `json.load(file)` and `json.loads(text)`</x:v>
+        <x:v>`day2_summary.txt`</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>Use `readlines()` for both</x:v>
+        <x:v>`day_final_sales.txt`</x:v>
       </x:c>
       <x:c r="Q33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="66" hidden="0" customHeight="1">
       <x:c r="A34" t="str">
         <x:v>Python - MCQ - 11.4.3</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>A program needs JSON text in memory to send elsewhere, not a JSON file on disk. Which function returns a string?</x:v>
+        <x:v>Make a saved JSON report readable to humans
+A nested JSON file will be inspected manually during an audit, so it should use readable line breaks and indentation.
+Which argument supplies that formatting during `json.dump`?</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>`json.dumps(object)` serializes a Python object to a JSON string. `json.dump` instead writes to an open file.</x:v>
+        <x:v>The optional `indent` argument pretty-prints nested JSON without changing its data.</x:v>
       </x:c>
       <x:c r="D34" t="n">
         <x:v>1</x:v>
@@ -2075,10 +2174,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H34" t="str">
         <x:v>python - Set 4</x:v>
@@ -2094,30 +2193,36 @@
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34" t="str">
-        <x:v>`json.load()`</x:v>
+        <x:v>`indent=4`</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>`json.dumps()`</x:v>
+        <x:v>`newline=""`</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>`csv.writer()`</x:v>
+        <x:v>`mode="pretty"`</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>`Path.write_text()`</x:v>
+        <x:v>`fieldnames=4`</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="132" hidden="0" customHeight="1">
       <x:c r="A35" t="str">
         <x:v>Python - MCQ - 11.4.4</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>A Python tuple is serialized to JSON and then loaded again. Which limitation matters if the program must preserve tuple identity?</x:v>
+        <x:v>Replace an entire small text report through a Path
+A short summary file should contain exactly the newest report text. No line-by-line processing or append behaviour is needed.
+```python
+from pathlib import Path
+report = Path("summary.txt")
+```
+Which operation directly writes the complete text?</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>JSON has arrays but no distinct tuple type. A Python tuple is saved as a JSON array and loads back as a list, so the distinction is lost.</x:v>
+        <x:v>`Path.write_text` writes an entire text value directly to the target path.</x:v>
       </x:c>
       <x:c r="D35" t="n">
         <x:v>1</x:v>
@@ -2126,10 +2231,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F35" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H35" t="str">
         <x:v>python - Set 4</x:v>
@@ -2141,34 +2246,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>json-processing</x:v>
+        <x:v>file-paths</x:v>
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35" t="str">
-        <x:v>The tuple becomes a JSON array and loads back as a list</x:v>
+        <x:v>`report.touch()` followed by `report.open()` with no write</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>JSON refuses all sequences</x:v>
+        <x:v>`report.read_text(encoding="utf-8")`</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>The tuple becomes a CSV row</x:v>
+        <x:v>`report.write_text("Ready", encoding="utf-8")`</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>Only the first tuple item is saved</x:v>
+        <x:v>`report.rename("Ready")`</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="66" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
         <x:v>Python - MCQ - 11.4.5</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>A project must store flat student rows for spreadsheet exchange and a nested application configuration. Which format choice best matches both shapes?</x:v>
+        <x:v>Prevent platform-specific blank lines in a CSV export
+A CSV writer produces extra blank rows on one teammate's operating system. The file was opened without the CSV-specific newline setting.
+Which opening style follows the lesson's recommended habit?</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>CSV suits flat rows and columns, while JSON naturally represents nested dictionaries and lists. Choosing by data shape avoids awkward manual encoding.</x:v>
+        <x:v>`newline=""` lets the CSV module manage row endings consistently across platforms.</x:v>
       </x:c>
       <x:c r="D36" t="n">
         <x:v>1</x:v>
@@ -2177,7 +2284,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F36" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G36" t="str">
         <x:v>analyze</x:v>
@@ -2192,34 +2299,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>json-processing</x:v>
+        <x:v>csv-processing</x:v>
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>Use CSV for both because it preserves all nested types</x:v>
+        <x:v>`open("sales.csv", "r")`</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Use JSON for the rows and plain text for the configuration</x:v>
+        <x:v>`open("sales.csv", "w", newline="\n", encoding="utf-8")`</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Use CSV for the student table and JSON for the nested configuration</x:v>
+        <x:v>`open("sales.csv", "a", encoding=None)`</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Use glob patterns as the storage format</x:v>
+        <x:v>`open("sales.csv", "w", newline="", encoding="utf-8")`</x:v>
       </x:c>
       <x:c r="Q36" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="66" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
         <x:v>Python - MCQ - 11.4.6</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>A script opens `missing.txt` in read mode without checking whether it exists. What failure should the developer expect?</x:v>
+        <x:v>Decide whether two complete-reading implementations are equivalent
+For an existing, small UTF-8 text file, Version A uses a managed `open` call and `read()`. Version B uses `Path.read_text` with the same encoding. Neither implementation needs streaming or access to the open file object.
+Which review conclusion is accurate?</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Read mode requires an existing file. If the path does not exist, `open` raises `FileNotFoundError` immediately.</x:v>
+        <x:v>Under the stated constraints, both implementations read the entire decoded text into one string and release the file resource; they differ mainly in interface.</x:v>
       </x:c>
       <x:c r="D37" t="n">
         <x:v>1</x:v>
@@ -2228,10 +2337,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F37" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H37" t="str">
         <x:v>python - Set 4</x:v>
@@ -2243,34 +2352,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>file-errors</x:v>
+        <x:v>file-operations</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>An empty file is always created</x:v>
+        <x:v>Version A returns a list of lines, while Version B returns bytes.</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>The read returns an empty string</x:v>
+        <x:v>Equivalent here: both return all text and close the file.</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>The path changes to the current folder</x:v>
+        <x:v>Version B necessarily appends an extra newline to the returned text.</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>A FileNotFoundError is raised</x:v>
+        <x:v>Version A leaves the file open after its `with` block.</x:v>
       </x:c>
       <x:c r="Q37" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="66" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>Python - MCQ - 11.4.7</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>A receipt containing `₹1500` must be written on one machine and read correctly on another. Which habit removes reliance on system-default encodings?</x:v>
+        <x:v>Design a restart-safe attendee tracker
+An attendee tracker must preserve IDs after shutdown, load them when the next run begins, and add later scans without erasing earlier ones.
+Which workflow satisfies all three needs?</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Explicitly using UTF-8 for both operations ensures the writer and reader interpret the same bytes as the same characters.</x:v>
+        <x:v>Reading restores persistent state, and append mode extends the stored history non-destructively.</x:v>
       </x:c>
       <x:c r="D38" t="n">
         <x:v>1</x:v>
@@ -2282,7 +2393,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>python - Set 4</x:v>
@@ -2294,34 +2405,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>file-errors</x:v>
+        <x:v>file-operations</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
-        <x:v>Specify `encoding='utf-8'` on both the write and read</x:v>
+        <x:v>Store IDs only in a set and print it before exit.</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>Use different encodings for each machine</x:v>
+        <x:v>Open the log in write mode for every scan.</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Remove the file extension</x:v>
+        <x:v>Load saved IDs at startup and append later scans.</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>Open the file twice in write mode</x:v>
+        <x:v>Recreate an empty variable at the start of every run.</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="66" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
         <x:v>Python - MCQ - 11.4.8</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>A CSV analyzer computes average CGPA from `DictReader` rows but receives a TypeError while adding values. Which repair addresses the data-model issue without changing the file?</x:v>
+        <x:v>Write dictionary rows with matching CSV columns
+A CSV export already has a `DictWriter` configured with `fieldnames`, has written its header, and now holds a list named `sales` containing dictionaries.
+Which call writes every dictionary as a row?</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>DictReader supplies CSV fields as strings. Converting each valid `row['cgpa']` to `float` before accumulation makes the average numeric; validation of missing values can be added around that conversion later.</x:v>
+        <x:v>`DictWriter.writerows` maps each dictionary's keys to the configured CSV fields.</x:v>
       </x:c>
       <x:c r="D39" t="n">
         <x:v>1</x:v>
@@ -2330,10 +2443,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F39" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>python - Set 4</x:v>
@@ -2349,30 +2462,32 @@
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39" t="str">
-        <x:v>Use append mode when opening the CSV</x:v>
+        <x:v>`writer.writerows(sales)`</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>Convert each CGPA string to `float` before summing</x:v>
+        <x:v>`writer.writerow(sales)`</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Serialize every row to JSON before reading it</x:v>
+        <x:v>`writer.writeheader()`</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>Replace the header with numeric column indexes</x:v>
+        <x:v>`writer.writerows(sales[0])`</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="66" hidden="0" customHeight="1">
       <x:c r="A40" t="str">
         <x:v>Python - MCQ - 11.4.9</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>A developer writes `open('notes.txt')` without a mode argument. Which mode does Python use by default?</x:v>
+        <x:v>Reject a format that cannot naturally preserve nesting
+A configuration contains dictionaries inside dictionaries, lists, numbers, booleans, and `None`. A proposed CSV export would flatten everything into manually encoded cells.
+Which design judgment is strongest?</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>The default mode for `open()` is read mode. The file must already exist, just as if the caller had written `open('notes.txt', 'r')`.</x:v>
+        <x:v>JSON models nested structured values directly, while CSV fundamentally represents rows and columns of text.</x:v>
       </x:c>
       <x:c r="D40" t="n">
         <x:v>1</x:v>
@@ -2381,10 +2496,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F40" t="str">
-        <x:v>easy</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>python - Set 4</x:v>
@@ -2396,34 +2511,36 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>file-operations</x:v>
+        <x:v>json-processing</x:v>
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40" t="str">
-        <x:v>Append mode</x:v>
+        <x:v>CSV automatically reconstructs arbitrary nesting and Python types.</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>Write mode</x:v>
+        <x:v>Plain `split(",")` preserves nested objects better than both modules.</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Read mode</x:v>
+        <x:v>Both formats preserve tuples as tuples with no special handling.</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>Binary write mode</x:v>
+        <x:v>Use JSON for the nesting; CSV would require custom flattening.</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="66" hidden="0" customHeight="1">
       <x:c r="A41" t="str">
         <x:v>Python - MCQ - 11.4.10</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>For `Path('reports/day1_sales.csv')`, a dashboard needs the containing folder rather than the filename or extension. Which property returns it?</x:v>
+        <x:v>Assemble a reliable daily-report pipeline
+A festival pipeline must create a reports folder safely, append text logs, export flat sales rows, save a nested summary, and tolerate a report that has not yet been generated.
+Which design best applies the full unit?</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>The `.parent` property returns the containing path, which is `reports` here. `.name`, `.stem`, and `.suffix` describe the final filename instead.</x:v>
+        <x:v>The design selects the safe path, mode, context management, format, and missing-file guard appropriate to each requirement.</x:v>
       </x:c>
       <x:c r="D41" t="n">
         <x:v>1</x:v>
@@ -2435,7 +2552,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H41" t="str">
         <x:v>python - Set 4</x:v>
@@ -2447,23 +2564,23 @@
         <x:v>file-handling</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>file-paths</x:v>
+        <x:v>file-errors</x:v>
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41" t="str">
-        <x:v>The `.name` property for the complete final filename</x:v>
+        <x:v>Build paths by string guessing, use write mode for every log entry, and parse all data with `split(",")`.</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>`.stem`</x:v>
+        <x:v>Use `Path`, `with`, append logs, CSV, JSON, and guarded reads.</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>`.suffix`</x:v>
+        <x:v>Keep everything only in variables and rely on program memory after restart.</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>`.parent`</x:v>
+        <x:v>Upload open file objects so another machine can continue using them.</x:v>
       </x:c>
       <x:c r="Q41" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
